--- a/docs/downloads/04/tbl_cm_read_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_read_sex_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -516,7 +516,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -820,7 +820,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -866,7 +866,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
